--- a/static/bw_amr_ig/all-profiles.xlsx
+++ b/static/bw_amr_ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
